--- a/tests/supervisionPackages/data/OGRS4 test inputs.xlsx
+++ b/tests/supervisionPackages/data/OGRS4 test inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martin.hoirns/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE5EEC9-94AF-CA48-970D-21FFDFAD0F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2196020-C0A1-6346-B72E-FEE0626205CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53480" yWindow="-300" windowWidth="50400" windowHeight="24900" activeTab="6" xr2:uid="{A754F796-5A0B-42E9-8362-A0C9C3BDEB7F}"/>
+    <workbookView xWindow="42480" yWindow="480" windowWidth="23920" windowHeight="18280" activeTab="6" xr2:uid="{A754F796-5A0B-42E9-8362-A0C9C3BDEB7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" state="hidden" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="355">
   <si>
     <t>Gender</t>
   </si>
@@ -1077,9 +1077,6 @@
     <t>Question</t>
   </si>
   <si>
-    <t>abc</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -1102,6 +1099,21 @@
   </si>
   <si>
     <t>Date of first sanction</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>In a relationship, living together</t>
+  </si>
+  <si>
+    <t>Not in a relationship</t>
+  </si>
+  <si>
+    <t>ZZJMFUD</t>
+  </si>
+  <si>
+    <t>ZEPCYUR</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1244,9 +1256,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1265,60 +1274,6 @@
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1448,6 +1403,60 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="none">
@@ -1535,15 +1544,15 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{B7FD7F90-B9E6-D740-A69E-0C07392D58CF}" name="Page" dataDxfId="12"/>
     <tableColumn id="22" xr3:uid="{E0F0B2C3-4ED9-CC42-B50D-F49021240890}" name="Question" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{3850F913-77DA-3844-9CC5-2082CBF8F378}" name="Description" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{51ABD908-CF4B-9243-979C-CD4DBD3E9353}" name="Type" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{0B551F59-817D-DC43-84D7-AAF7E22E00D4}" name="ARP static" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{DC1D60F8-4277-1D41-BD35-1606D82BB1A8}" name="ARP dynamic" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{A4CA7FA9-3E65-5246-9CD5-5862CE73DB59}" name="CSRP static" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{6A3ADD5C-9A43-4745-9FB6-1BC3067E45AA}" name="CSRP dynamic" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{D5EA6900-E571-1F4B-A548-4AD451974DE7}" name="DC-SRP" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{E79F8657-8B31-4C41-8208-38DBAD0441AA}" name="Test 1" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{736773D4-BB12-F749-A2E3-EB2276BD8F76}" name="Test 2" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{3850F913-77DA-3844-9CC5-2082CBF8F378}" name="Description" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{51ABD908-CF4B-9243-979C-CD4DBD3E9353}" name="Type" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{0B551F59-817D-DC43-84D7-AAF7E22E00D4}" name="ARP static" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{DC1D60F8-4277-1D41-BD35-1606D82BB1A8}" name="ARP dynamic" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{A4CA7FA9-3E65-5246-9CD5-5862CE73DB59}" name="CSRP static" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{6A3ADD5C-9A43-4745-9FB6-1BC3067E45AA}" name="CSRP dynamic" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{D5EA6900-E571-1F4B-A548-4AD451974DE7}" name="DC-SRP" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{E79F8657-8B31-4C41-8208-38DBAD0441AA}" name="Test 1" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{736773D4-BB12-F749-A2E3-EB2276BD8F76}" name="Test 2" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2948,7 +2957,7 @@
         <v>228</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>98</v>
@@ -2985,10 +2994,10 @@
       <c r="H2" s="8"/>
       <c r="I2" s="23"/>
       <c r="J2" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="K2" s="8">
-        <v>123</v>
+        <v>354</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -2999,10 +3008,10 @@
         <v>234</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>103</v>
@@ -3037,7 +3046,7 @@
         <v>240</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>103</v>
@@ -3072,7 +3081,7 @@
         <v>241</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>102</v>
@@ -3107,7 +3116,7 @@
         <v>242</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>103</v>
@@ -3140,7 +3149,7 @@
         <v>243</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>102</v>
@@ -3175,7 +3184,7 @@
         <v>244</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>102</v>
@@ -3206,7 +3215,7 @@
         <v>245</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>102</v>
@@ -3237,7 +3246,7 @@
         <v>246</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>102</v>
@@ -3268,7 +3277,7 @@
         <v>247</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>102</v>
@@ -3299,7 +3308,7 @@
         <v>248</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>102</v>
@@ -3330,7 +3339,7 @@
         <v>249</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>102</v>
@@ -3361,7 +3370,7 @@
         <v>250</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>102</v>
@@ -3392,7 +3401,7 @@
         <v>251</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>103</v>
@@ -3427,7 +3436,7 @@
         <v>252</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>102</v>
@@ -3458,7 +3467,7 @@
         <v>253</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>102</v>
@@ -3493,7 +3502,7 @@
         <v>254</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>102</v>
@@ -3528,7 +3537,7 @@
         <v>255</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>102</v>
@@ -3563,7 +3572,7 @@
         <v>256</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>102</v>
@@ -3595,7 +3604,7 @@
         <v>257</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>102</v>
@@ -3612,7 +3621,7 @@
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>327</v>
       </c>
@@ -3623,7 +3632,7 @@
         <v>258</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>102</v>
@@ -3641,10 +3650,10 @@
         <v>102</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -3658,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>102</v>
@@ -3690,10 +3699,10 @@
         <v>339</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="12" t="s">
@@ -3714,7 +3723,7 @@
         <v>276</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>102</v>
@@ -3742,7 +3751,7 @@
         <v>277</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>102</v>
@@ -3773,7 +3782,7 @@
         <v>278</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>102</v>
@@ -3804,7 +3813,7 @@
         <v>279</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>102</v>
@@ -3835,7 +3844,7 @@
         <v>280</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>102</v>
@@ -3863,7 +3872,7 @@
         <v>281</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>102</v>
@@ -3894,7 +3903,7 @@
         <v>282</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>102</v>
@@ -3925,7 +3934,7 @@
         <v>283</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>102</v>
@@ -3956,7 +3965,7 @@
         <v>284</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>102</v>
@@ -3984,7 +3993,7 @@
         <v>285</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>102</v>
@@ -4015,7 +4024,7 @@
         <v>286</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>102</v>
@@ -4046,7 +4055,7 @@
         <v>287</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>102</v>
@@ -4077,7 +4086,7 @@
         <v>288</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>102</v>
@@ -4108,7 +4117,7 @@
         <v>289</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>102</v>
@@ -4139,7 +4148,7 @@
         <v>290</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>102</v>
@@ -4170,7 +4179,7 @@
         <v>291</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>102</v>
@@ -4201,7 +4210,7 @@
         <v>292</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>102</v>
@@ -4232,7 +4241,7 @@
         <v>293</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>102</v>
@@ -4262,8 +4271,8 @@
       <c r="C43" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="D43" s="26" t="s">
-        <v>344</v>
+      <c r="D43" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>102</v>
@@ -4291,7 +4300,7 @@
         <v>295</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>102</v>
@@ -4319,7 +4328,7 @@
         <v>296</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>102</v>
@@ -4350,7 +4359,7 @@
         <v>297</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>102</v>
@@ -4372,7 +4381,7 @@
     </row>
     <row r="47" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>330</v>
@@ -4381,7 +4390,7 @@
         <v>298</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>102</v>
@@ -4398,12 +4407,16 @@
       <c r="I47" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
+      <c r="J47" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>331</v>
@@ -4412,7 +4425,7 @@
         <v>18</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>102</v>
@@ -4429,12 +4442,16 @@
       <c r="I48" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
+      <c r="J48" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>332</v>
@@ -4443,7 +4460,7 @@
         <v>299</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>102</v>
@@ -4460,12 +4477,16 @@
       <c r="I49" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
+      <c r="J49" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>333</v>
@@ -4474,7 +4495,7 @@
         <v>300</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>102</v>
@@ -4491,12 +4512,16 @@
       <c r="I50" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
+      <c r="J50" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="51" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>334</v>
@@ -4505,7 +4530,7 @@
         <v>301</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>102</v>
@@ -4522,12 +4547,16 @@
       <c r="I51" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
+      <c r="J51" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>335</v>
@@ -4536,7 +4565,7 @@
         <v>302</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>102</v>
@@ -4553,12 +4582,16 @@
       <c r="I52" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
+      <c r="J52" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>336</v>
@@ -4567,7 +4600,7 @@
         <v>303</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>102</v>
@@ -4584,12 +4617,16 @@
       <c r="I53" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
+      <c r="J53" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>337</v>
@@ -4598,7 +4635,7 @@
         <v>17</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>102</v>
@@ -4615,12 +4652,16 @@
       <c r="I54" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
+      <c r="J54" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>338</v>
@@ -4629,7 +4670,7 @@
         <v>304</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>102</v>
@@ -4646,8 +4687,12 @@
       <c r="I55" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
+      <c r="J55" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="K55" s="12" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="17"/>
@@ -7611,15 +7656,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100710E1FBEF1A5B948A87C0B389DC5DB2E" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fbe41d5b9331aa7762730bdafbbb9fca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2715bc29-68cb-4af3-883a-7773fe7844be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e4a3e70597ee21988b5dcb00eb88438a" ns2:_="">
     <xsd:import namespace="2715bc29-68cb-4af3-883a-7773fe7844be"/>
@@ -7757,6 +7793,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED3A4330-F882-48EB-84A6-4C413EAC9C8A}">
   <ds:schemaRefs>
@@ -7774,14 +7819,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02199C31-48B1-490B-A194-08D98129BC48}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C532450E-AFC7-45D1-9C83-D535664516A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7797,4 +7834,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02199C31-48B1-490B-A194-08D98129BC48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/supervisionPackages/data/OGRS4 test inputs.xlsx
+++ b/tests/supervisionPackages/data/OGRS4 test inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martin.hoirns/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE7680B-78BE-C241-B1D6-4FDB0FF9649E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD0F01D-D7D6-6C47-BFA9-2A1133A41C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="62520" yWindow="-180" windowWidth="44500" windowHeight="24900" activeTab="6" xr2:uid="{A754F796-5A0B-42E9-8362-A0C9C3BDEB7F}"/>
   </bookViews>
@@ -20,14 +20,16 @@
     <sheet name="OSP-IIC" sheetId="5" state="hidden" r:id="rId5"/>
     <sheet name="IIC DC Comparison" sheetId="8" state="hidden" r:id="rId6"/>
     <sheet name="CRNs" sheetId="12" r:id="rId7"/>
-    <sheet name="Test data" sheetId="9" r:id="rId8"/>
-    <sheet name="Ref" sheetId="13" r:id="rId9"/>
-    <sheet name="AAED Workout" sheetId="11" state="hidden" r:id="rId10"/>
-    <sheet name="Unused Questions" sheetId="10" state="hidden" r:id="rId11"/>
+    <sheet name="Male" sheetId="9" r:id="rId8"/>
+    <sheet name="Female" sheetId="14" r:id="rId9"/>
+    <sheet name="Ref" sheetId="13" r:id="rId10"/>
+    <sheet name="AAED Workout" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="Unused Questions" sheetId="10" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Unused Questions'!$A$1:$H$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Unused Questions'!$A$1:$H$90</definedName>
     <definedName name="assessmentTypes">Ref!$A$2:$A$5</definedName>
+    <definedName name="scenarios" localSheetId="8">Table24[[#Headers],[Missing]:[G prov]]</definedName>
     <definedName name="scenarios">Table2[[#Headers],[Missing]:[G prov]]</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="403">
   <si>
     <t>Gender</t>
   </si>
@@ -1249,6 +1251,18 @@
   </si>
   <si>
     <t>Date of first sanction</t>
+  </si>
+  <si>
+    <t>ZMPCTPO</t>
+  </si>
+  <si>
+    <t>2-Significant problems</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Daily</t>
   </si>
 </sst>
 </file>
@@ -1417,12 +1431,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill>
@@ -1436,6 +1450,410 @@
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1454,20 +1872,75 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1949,6 +2422,38 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1971,9 +2476,9 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F066904D-D1F8-C945-A53F-4F736D74C46E}" name="CRN" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F066904D-D1F8-C945-A53F-4F736D74C46E}" name="CRN" dataDxfId="55"/>
     <tableColumn id="2" xr3:uid="{41D0AD11-A958-224F-A336-689C472DBC80}" name="Type"/>
-    <tableColumn id="3" xr3:uid="{3BAEAE25-CE10-2B42-B714-24D32A45BB8D}" name="Scenario" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{3BAEAE25-CE10-2B42-B714-24D32A45BB8D}" name="Scenario" dataDxfId="54"/>
     <tableColumn id="4" xr3:uid="{84A1DD91-19B4-814D-8C47-DD33291E322C}" name="User"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
@@ -1981,31 +2486,62 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F34C0681-7709-AB4D-BDDE-42A72C057A2D}" name="Table2" displayName="Table2" ref="A1:W63" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F34C0681-7709-AB4D-BDDE-42A72C057A2D}" name="Table2" displayName="Table2" ref="A1:W63" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <tableColumns count="23">
-    <tableColumn id="22" xr3:uid="{E0F0B2C3-4ED9-CC42-B50D-F49021240890}" name="Question" dataDxfId="25"/>
-    <tableColumn id="23" xr3:uid="{3850F913-77DA-3844-9CC5-2082CBF8F378}" name="Description" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{51ABD908-CF4B-9243-979C-CD4DBD3E9353}" name="Type" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{0B551F59-817D-DC43-84D7-AAF7E22E00D4}" name="ARP static" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{DC1D60F8-4277-1D41-BD35-1606D82BB1A8}" name="ARP dynamic" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{A4CA7FA9-3E65-5246-9CD5-5862CE73DB59}" name="CSRP static" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{6A3ADD5C-9A43-4745-9FB6-1BC3067E45AA}" name="CSRP dynamic" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{D5EA6900-E571-1F4B-A548-4AD451974DE7}" name="DC-SRP" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{E79F8657-8B31-4C41-8208-38DBAD0441AA}" name="Missing" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{4DAF20FC-296B-A64F-94B8-BE75CBC5F2DB}" name="A" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{FE049268-B947-E241-8D5D-1D9413DD160A}" name="B" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{CD3FE3A1-80D9-404C-81B8-026CAE5B1688}" name="C" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{24E869DA-3BBF-6D41-A742-1FB2D9EEBC5D}" name="D" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{06A1BF28-CA98-D149-BAA8-0298A042696B}" name="E" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{A8253064-9F68-C643-A2A1-9CDDD0BA1108}" name="F" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{02BEA690-CB36-BA45-9934-7696A37E40F1}" name="G" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{736773D4-BB12-F749-A2E3-EB2276BD8F76}" name="A prov" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{245C5926-254A-0648-A49E-B4AB9B1D3B0A}" name="B prov" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{6B369F43-5FE5-8F4C-8050-E84D13639628}" name="C prov" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{F89B2296-1452-2D45-90E9-9F4470860E08}" name="D prov" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{367106C5-CD76-C74F-BFA4-D9159401B598}" name="E prov" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{0AAE6E5F-3B25-5F48-B262-2A376EDA38E0}" name="F prov" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{4475BADB-2081-BB47-A276-69112F7BE4F1}" name="G prov" dataDxfId="3"/>
+    <tableColumn id="22" xr3:uid="{E0F0B2C3-4ED9-CC42-B50D-F49021240890}" name="Question" dataDxfId="51"/>
+    <tableColumn id="23" xr3:uid="{3850F913-77DA-3844-9CC5-2082CBF8F378}" name="Description" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{51ABD908-CF4B-9243-979C-CD4DBD3E9353}" name="Type" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{0B551F59-817D-DC43-84D7-AAF7E22E00D4}" name="ARP static" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{DC1D60F8-4277-1D41-BD35-1606D82BB1A8}" name="ARP dynamic" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{A4CA7FA9-3E65-5246-9CD5-5862CE73DB59}" name="CSRP static" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{6A3ADD5C-9A43-4745-9FB6-1BC3067E45AA}" name="CSRP dynamic" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{D5EA6900-E571-1F4B-A548-4AD451974DE7}" name="DC-SRP" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{E79F8657-8B31-4C41-8208-38DBAD0441AA}" name="Missing" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{4DAF20FC-296B-A64F-94B8-BE75CBC5F2DB}" name="A" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{FE049268-B947-E241-8D5D-1D9413DD160A}" name="B" dataDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{CD3FE3A1-80D9-404C-81B8-026CAE5B1688}" name="C" dataDxfId="40"/>
+    <tableColumn id="19" xr3:uid="{24E869DA-3BBF-6D41-A742-1FB2D9EEBC5D}" name="D" dataDxfId="39"/>
+    <tableColumn id="20" xr3:uid="{06A1BF28-CA98-D149-BAA8-0298A042696B}" name="E" dataDxfId="38"/>
+    <tableColumn id="21" xr3:uid="{A8253064-9F68-C643-A2A1-9CDDD0BA1108}" name="F" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{02BEA690-CB36-BA45-9934-7696A37E40F1}" name="G" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{736773D4-BB12-F749-A2E3-EB2276BD8F76}" name="A prov" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{245C5926-254A-0648-A49E-B4AB9B1D3B0A}" name="B prov" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{6B369F43-5FE5-8F4C-8050-E84D13639628}" name="C prov" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{F89B2296-1452-2D45-90E9-9F4470860E08}" name="D prov" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{367106C5-CD76-C74F-BFA4-D9159401B598}" name="E prov" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{0AAE6E5F-3B25-5F48-B262-2A376EDA38E0}" name="F prov" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{4475BADB-2081-BB47-A276-69112F7BE4F1}" name="G prov" dataDxfId="29"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00D59CCA-7D59-934B-B625-EABFDE80864F}" name="Table24" displayName="Table24" ref="A1:W63" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+  <tableColumns count="23">
+    <tableColumn id="22" xr3:uid="{DD0E608D-38A1-6C41-B752-8CEDD76DE22B}" name="Question" dataDxfId="26"/>
+    <tableColumn id="23" xr3:uid="{80F90AE0-0153-4C47-9BBE-350E7DE6BACA}" name="Description" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{3A0CBB6A-38B0-844C-90BE-F5CD6319D3BC}" name="Type" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{D6ACD4C9-4694-8A4D-A13D-3F609C582F04}" name="ARP static" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{C6D0DF86-7F83-C64E-A394-1C2E0BFF958E}" name="ARP dynamic" dataDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{58E88C10-D8D4-514A-82E4-8C6FADF93FF6}" name="CSRP static" dataDxfId="21"/>
+    <tableColumn id="17" xr3:uid="{C37472D7-79FC-D24A-AD4B-9BC8CAF1335B}" name="CSRP dynamic" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{E13B6D10-0490-D540-A858-F2830D9C266B}" name="DC-SRP" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{862A24B0-EB4C-234A-9DA6-2AA57DAB9604}" name="Missing" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{D1EDDE3C-AA95-3849-9476-ED1FB55EFE44}" name="A" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{D3F9E6CF-B940-5E44-86D0-A5FE36663B01}" name="B" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{96CF3831-6757-4247-B840-43EAB854255F}" name="C" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{D0AF7064-553A-5141-A3B4-A6334E6B7D44}" name="D" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{876B2562-276C-CE41-9B0C-AA5123EAC9F1}" name="E" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{8ACCD7BC-DC74-E848-AA82-AB9C2C766D3A}" name="F" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{F2EE81ED-DA20-DE4E-BB85-A4D2044929C1}" name="G" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{6A9EF48A-30DC-E641-B97B-97E73C8CEF9A}" name="A prov" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{17F8A51E-E3F2-AB43-86EB-E60E9F3CE232}" name="B prov" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{37C18CAE-8DF2-D346-8765-EE38286E86C6}" name="C prov" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{D925ABB4-A97C-0B48-8148-D1A40A6F789D}" name="D prov" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{0E5B7D11-BCD1-654A-90E5-272D643D9761}" name="E prov" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{8055184B-1896-3146-9771-16B1445BCC11}" name="F prov" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{607CDEBB-DBDA-6448-A1D7-146E679C54F6}" name="G prov" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2430,6 +2966,44 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BB45B6-2F73-1246-8596-5A0FAE6B734B}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C0FA8A-FDCF-457B-9547-0B10EAC6AC6E}">
   <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2547,7 +3121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E184558-BC56-4490-BC9C-536AF1B83C09}">
   <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6241,14 +6815,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E22DE4A-C128-6440-A468-AE858B801CD8}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="47.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>334</v>
       </c>
@@ -6264,13 +6838,19 @@
       <c r="F1" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>344</v>
       </c>
       <c r="B2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C2" t="s">
         <v>363</v>
@@ -6281,13 +6861,19 @@
       <c r="F2" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J2" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="L2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
         <v>350</v>
       </c>
       <c r="B3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C3" t="s">
         <v>379</v>
@@ -6295,13 +6881,16 @@
       <c r="D3" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J3" s="26" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
         <v>351</v>
       </c>
       <c r="B4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C4" t="s">
         <v>380</v>
@@ -6309,13 +6898,16 @@
       <c r="D4" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J4" s="26" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
         <v>352</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C5" t="s">
         <v>381</v>
@@ -6323,13 +6915,16 @@
       <c r="D5" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J5" s="26" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
         <v>353</v>
       </c>
       <c r="B6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C6" t="s">
         <v>382</v>
@@ -6337,13 +6932,16 @@
       <c r="D6" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J6" s="26" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="26" t="s">
         <v>354</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C7" t="s">
         <v>383</v>
@@ -6351,13 +6949,16 @@
       <c r="D7" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J7" s="26" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="26" t="s">
         <v>355</v>
       </c>
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8" t="s">
         <v>384</v>
@@ -6365,13 +6966,16 @@
       <c r="D8" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J8" s="26" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="26" t="s">
         <v>356</v>
       </c>
       <c r="B9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C9" t="s">
         <v>385</v>
@@ -6379,13 +6983,16 @@
       <c r="D9" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J9" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
         <v>357</v>
       </c>
       <c r="B10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C10" t="s">
         <v>372</v>
@@ -6393,13 +7000,16 @@
       <c r="D10" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J10" s="26" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="26" t="s">
         <v>358</v>
       </c>
       <c r="B11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C11" t="s">
         <v>373</v>
@@ -6407,13 +7017,16 @@
       <c r="D11" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J11" s="26" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="26" t="s">
         <v>359</v>
       </c>
       <c r="B12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C12" t="s">
         <v>374</v>
@@ -6421,13 +7034,16 @@
       <c r="D12" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J12" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
         <v>360</v>
       </c>
       <c r="B13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C13" t="s">
         <v>375</v>
@@ -6435,13 +7051,16 @@
       <c r="D13" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J13" s="26" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="26" t="s">
         <v>361</v>
       </c>
       <c r="B14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C14" t="s">
         <v>376</v>
@@ -6449,13 +7068,16 @@
       <c r="D14" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J14" s="26" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="26" t="s">
         <v>362</v>
       </c>
       <c r="B15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C15" t="s">
         <v>377</v>
@@ -6463,19 +7085,25 @@
       <c r="D15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="J15" s="26" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="26" t="s">
         <v>345</v>
       </c>
       <c r="B16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C16" t="s">
         <v>378</v>
       </c>
       <c r="D16" t="s">
         <v>366</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -10379,12 +11007,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A9:W15 A17:W17">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>A$8="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:W42">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>A$25="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10397,115 +11025,3900 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BB45B6-2F73-1246-8596-5A0FAE6B734B}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4EED5-4AD9-8E47-BA96-6997233E6EE6}">
+  <dimension ref="A1:AA66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9" style="11" customWidth="1"/>
+    <col min="2" max="2" width="59.5" style="11" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="11" customWidth="1"/>
+    <col min="5" max="8" width="9.6640625" style="12" customWidth="1"/>
+    <col min="9" max="20" width="14" style="12" customWidth="1"/>
+    <col min="28" max="16384" width="10.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>396</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>393</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>394</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F6" s="26" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F7" s="26" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F8" s="26" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F9" s="26" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F10" s="26" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F11" s="26" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F12" s="26" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F13" s="26" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F14" s="26" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F15" s="26" t="s">
-        <v>345</v>
-      </c>
+    <row r="1" spans="1:27" s="8" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" s="22" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="T2" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="W2" s="20" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="22" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="R3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="T3" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="U3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="W3" s="20" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="J4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="K4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="L4" s="11">
+        <v>-120</v>
+      </c>
+      <c r="M4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="N4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="O4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="P4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="R4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="S4" s="11">
+        <v>-120</v>
+      </c>
+      <c r="T4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="U4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="V4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="W4" s="11">
+        <v>-60</v>
+      </c>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+    </row>
+    <row r="5" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>1.32</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11">
+        <v>50</v>
+      </c>
+      <c r="K5" s="11">
+        <v>45</v>
+      </c>
+      <c r="L5" s="11">
+        <v>15</v>
+      </c>
+      <c r="M5" s="11">
+        <v>15</v>
+      </c>
+      <c r="N5" s="11">
+        <v>4</v>
+      </c>
+      <c r="O5" s="11">
+        <v>3</v>
+      </c>
+      <c r="P5" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>70</v>
+      </c>
+      <c r="R5" s="11">
+        <v>25</v>
+      </c>
+      <c r="S5" s="11">
+        <v>30</v>
+      </c>
+      <c r="T5" s="11">
+        <v>25</v>
+      </c>
+      <c r="U5" s="11">
+        <v>4</v>
+      </c>
+      <c r="V5" s="11">
+        <v>2</v>
+      </c>
+      <c r="W5" s="11">
+        <v>1</v>
+      </c>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+    </row>
+    <row r="6" spans="1:27" s="13" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11">
+        <v>15</v>
+      </c>
+      <c r="L6" s="11">
+        <v>5</v>
+      </c>
+      <c r="M6" s="11">
+        <v>5</v>
+      </c>
+      <c r="N6" s="11">
+        <v>2</v>
+      </c>
+      <c r="O6" s="11">
+        <v>1</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>60</v>
+      </c>
+      <c r="R6" s="11">
+        <v>10</v>
+      </c>
+      <c r="S6" s="11">
+        <v>15</v>
+      </c>
+      <c r="T6" s="11">
+        <v>10</v>
+      </c>
+      <c r="U6" s="11">
+        <v>2</v>
+      </c>
+      <c r="V6" s="11">
+        <v>1</v>
+      </c>
+      <c r="W6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="L7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="M7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="N7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="O7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="P7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="R7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="S7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="T7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="U7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="V7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="W7" s="11">
+        <v>-1</v>
+      </c>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+    </row>
+    <row r="8" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+    </row>
+    <row r="9" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="12"/>
+    </row>
+    <row r="10" spans="1:27" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+    </row>
+    <row r="11" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="K11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="L11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="R11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="S11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
+    </row>
+    <row r="12" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11">
+        <v>4</v>
+      </c>
+      <c r="K12" s="11">
+        <v>3</v>
+      </c>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11">
+        <v>4</v>
+      </c>
+      <c r="R12" s="11">
+        <v>2</v>
+      </c>
+      <c r="S12" s="11">
+        <v>1</v>
+      </c>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12"/>
+      <c r="AA12" s="12"/>
+    </row>
+    <row r="13" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11">
+        <v>3</v>
+      </c>
+      <c r="K13" s="11">
+        <v>2</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11">
+        <v>3</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+      <c r="AA13" s="12"/>
+    </row>
+    <row r="14" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11">
+        <v>2</v>
+      </c>
+      <c r="K14" s="11">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+      <c r="S14" s="11">
+        <v>0</v>
+      </c>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12"/>
+      <c r="AA14" s="12"/>
+    </row>
+    <row r="15" spans="1:27" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11">
+        <v>0</v>
+      </c>
+      <c r="R15" s="11">
+        <v>0</v>
+      </c>
+      <c r="S15" s="11">
+        <v>0</v>
+      </c>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+    </row>
+    <row r="16" spans="1:27" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="K16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="L16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="M16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="O16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="P16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="R16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="S16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="T16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="U16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="V16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="W16" s="11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="12"/>
+      <c r="AA17" s="12"/>
+    </row>
+    <row r="18" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+    </row>
+    <row r="19" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+      <c r="AA19" s="12"/>
+    </row>
+    <row r="20" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="R20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+    </row>
+    <row r="21" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
+      <c r="AA21" s="12"/>
+    </row>
+    <row r="22" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="R22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
+      <c r="AA22" s="12"/>
+    </row>
+    <row r="23" spans="1:27" ht="64" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="R23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+    </row>
+    <row r="24" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="12"/>
+    </row>
+    <row r="25" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="12"/>
+      <c r="AA25" s="12"/>
+    </row>
+    <row r="26" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="12"/>
+    </row>
+    <row r="27" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
+      <c r="AA27" s="12"/>
+    </row>
+    <row r="28" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
+      <c r="AA28" s="12"/>
+    </row>
+    <row r="29" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
+      <c r="AA29" s="12"/>
+    </row>
+    <row r="30" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+      <c r="AA30" s="12"/>
+    </row>
+    <row r="31" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="11"/>
+      <c r="V31" s="11"/>
+      <c r="W31" s="11"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
+      <c r="AA31" s="12"/>
+    </row>
+    <row r="32" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="12"/>
+    </row>
+    <row r="33" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="11"/>
+      <c r="V33" s="11"/>
+      <c r="W33" s="11"/>
+      <c r="X33" s="12"/>
+      <c r="Y33" s="12"/>
+      <c r="Z33" s="12"/>
+      <c r="AA33" s="12"/>
+    </row>
+    <row r="34" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="12"/>
+      <c r="Y34" s="12"/>
+      <c r="Z34" s="12"/>
+      <c r="AA34" s="12"/>
+    </row>
+    <row r="35" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="12"/>
+      <c r="Z35" s="12"/>
+      <c r="AA35" s="12"/>
+    </row>
+    <row r="36" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="11"/>
+      <c r="V36" s="11"/>
+      <c r="W36" s="11"/>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+      <c r="AA36" s="12"/>
+    </row>
+    <row r="37" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="12"/>
+      <c r="AA37" s="12"/>
+    </row>
+    <row r="38" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+      <c r="AA38" s="12"/>
+    </row>
+    <row r="39" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="12"/>
+      <c r="Y39" s="12"/>
+      <c r="Z39" s="12"/>
+      <c r="AA39" s="12"/>
+    </row>
+    <row r="40" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="11"/>
+      <c r="W40" s="11"/>
+      <c r="X40" s="12"/>
+      <c r="Y40" s="12"/>
+      <c r="Z40" s="12"/>
+      <c r="AA40" s="12"/>
+    </row>
+    <row r="41" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="12"/>
+      <c r="Y41" s="12"/>
+      <c r="Z41" s="12"/>
+      <c r="AA41" s="12"/>
+    </row>
+    <row r="42" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11"/>
+      <c r="V42" s="11"/>
+      <c r="W42" s="11"/>
+      <c r="X42" s="12"/>
+      <c r="Y42" s="12"/>
+      <c r="Z42" s="12"/>
+      <c r="AA42" s="12"/>
+    </row>
+    <row r="43" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A43" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q43" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="T43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V43" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="W43" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X43" s="12"/>
+      <c r="Y43" s="12"/>
+      <c r="Z43" s="12"/>
+      <c r="AA43" s="12"/>
+    </row>
+    <row r="44" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G44" s="11"/>
+      <c r="H44" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="N44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q44" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S44" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="T44" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="U44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W44" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X44" s="12"/>
+      <c r="Y44" s="12"/>
+      <c r="Z44" s="12"/>
+      <c r="AA44" s="12"/>
+    </row>
+    <row r="45" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="N45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q45" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S45" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="T45" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="U45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W45" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
+      <c r="AA45" s="12"/>
+    </row>
+    <row r="46" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A46" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q46" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="T46" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="U46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12"/>
+      <c r="AA46" s="12"/>
+    </row>
+    <row r="47" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="N47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="O47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q47" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="R47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="T47" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="U47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="V47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W47" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="12"/>
+      <c r="AA47" s="12"/>
+    </row>
+    <row r="48" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q48" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S48" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="T48" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="U48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W48" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X48" s="12"/>
+      <c r="Y48" s="12"/>
+      <c r="Z48" s="12"/>
+      <c r="AA48" s="12"/>
+    </row>
+    <row r="49" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q49" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S49" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="T49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W49" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X49" s="12"/>
+      <c r="Y49" s="12"/>
+      <c r="Z49" s="12"/>
+      <c r="AA49" s="12"/>
+    </row>
+    <row r="50" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q50" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S50" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="T50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W50" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X50" s="12"/>
+      <c r="Y50" s="12"/>
+      <c r="Z50" s="12"/>
+      <c r="AA50" s="12"/>
+    </row>
+    <row r="51" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q51" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S51" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="T51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X51" s="12"/>
+      <c r="Y51" s="12"/>
+      <c r="Z51" s="12"/>
+      <c r="AA51" s="12"/>
+    </row>
+    <row r="52" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q52" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X52" s="12"/>
+      <c r="Y52" s="12"/>
+      <c r="Z52" s="12"/>
+      <c r="AA52" s="12"/>
+    </row>
+    <row r="53" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q53" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X53" s="12"/>
+      <c r="Y53" s="12"/>
+      <c r="Z53" s="12"/>
+      <c r="AA53" s="12"/>
+    </row>
+    <row r="54" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H54" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q54" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X54" s="12"/>
+      <c r="Y54" s="12"/>
+      <c r="Z54" s="12"/>
+      <c r="AA54" s="12"/>
+    </row>
+    <row r="55" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q55" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="T55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X55" s="12"/>
+      <c r="Y55" s="12"/>
+      <c r="Z55" s="12"/>
+      <c r="AA55" s="12"/>
+    </row>
+    <row r="56" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="N56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="O56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="P56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="S56" s="11"/>
+      <c r="T56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="U56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="V56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="W56" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="X56" s="12"/>
+      <c r="Y56" s="12"/>
+      <c r="Z56" s="12"/>
+      <c r="AA56" s="12"/>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="23"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="11"/>
+      <c r="W57" s="11"/>
+      <c r="X57" s="12"/>
+      <c r="Y57" s="12"/>
+      <c r="Z57" s="12"/>
+      <c r="AA57" s="12"/>
+    </row>
+    <row r="58" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="9"/>
+      <c r="B58" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C58" s="23"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="J58" s="11">
+        <v>81.83</v>
+      </c>
+      <c r="K58" s="11">
+        <v>76</v>
+      </c>
+      <c r="L58" s="11">
+        <v>52.31</v>
+      </c>
+      <c r="M58" s="11">
+        <v>66.09</v>
+      </c>
+      <c r="N58" s="11">
+        <v>25.55</v>
+      </c>
+      <c r="O58" s="11">
+        <v>25.12</v>
+      </c>
+      <c r="P58" s="11">
+        <v>5.62</v>
+      </c>
+      <c r="Q58" s="16">
+        <v>88.8</v>
+      </c>
+      <c r="R58" s="11">
+        <v>81.849999999999994</v>
+      </c>
+      <c r="S58" s="11">
+        <v>71.56</v>
+      </c>
+      <c r="T58" s="11">
+        <v>71.41</v>
+      </c>
+      <c r="U58" s="11">
+        <v>39.36</v>
+      </c>
+      <c r="V58" s="11">
+        <v>19.13</v>
+      </c>
+      <c r="W58" s="11">
+        <v>6.07</v>
+      </c>
+      <c r="X58" s="12"/>
+      <c r="Y58" s="12"/>
+      <c r="Z58" s="12"/>
+      <c r="AA58" s="12"/>
+    </row>
+    <row r="59" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="9"/>
+      <c r="B59" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="23"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="J59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P59" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X59" s="12"/>
+      <c r="Y59" s="12"/>
+      <c r="Z59" s="12"/>
+      <c r="AA59" s="12"/>
+    </row>
+    <row r="60" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="9"/>
+      <c r="B60" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C60" s="23"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="J60" s="11">
+        <v>9.52</v>
+      </c>
+      <c r="K60" s="11">
+        <v>5.54</v>
+      </c>
+      <c r="L60" s="11">
+        <v>4.16</v>
+      </c>
+      <c r="M60" s="11">
+        <v>1.87</v>
+      </c>
+      <c r="N60" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="O60" s="11">
+        <v>0.41</v>
+      </c>
+      <c r="P60" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="Q60" s="11">
+        <v>8.33</v>
+      </c>
+      <c r="R60" s="11">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="S60" s="11">
+        <v>3.02</v>
+      </c>
+      <c r="T60" s="11">
+        <v>2.81</v>
+      </c>
+      <c r="U60" s="11">
+        <v>1.02</v>
+      </c>
+      <c r="V60" s="11">
+        <v>0.63</v>
+      </c>
+      <c r="W60" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="X60" s="12"/>
+      <c r="Y60" s="12"/>
+      <c r="Z60" s="12"/>
+      <c r="AA60" s="12"/>
+    </row>
+    <row r="61" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="9"/>
+      <c r="B61" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="23"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="J61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P61" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="12"/>
+      <c r="Z61" s="12"/>
+      <c r="AA61" s="12"/>
+    </row>
+    <row r="62" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="9"/>
+      <c r="B62" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C62" s="23"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="N62" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="O62" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="P62" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q62" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="R62" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="S62" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="T62" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="V62" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="W62" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
+      <c r="Z62" s="12"/>
+      <c r="AA62" s="12"/>
+    </row>
+    <row r="63" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="9"/>
+      <c r="B63" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C63" s="23"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="J63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X63" s="12"/>
+      <c r="Y63" s="12"/>
+      <c r="Z63" s="12"/>
+      <c r="AA63" s="12"/>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="U64" s="12"/>
+      <c r="V64" s="12"/>
+      <c r="W64" s="12"/>
+      <c r="X64" s="12"/>
+      <c r="Y64" s="12"/>
+      <c r="Z64" s="12"/>
+      <c r="AA64" s="12"/>
+    </row>
+    <row r="65" spans="21:27" x14ac:dyDescent="0.2">
+      <c r="U65" s="12"/>
+      <c r="V65" s="12"/>
+      <c r="W65" s="12"/>
+      <c r="X65" s="12"/>
+      <c r="Y65" s="12"/>
+      <c r="Z65" s="12"/>
+      <c r="AA65" s="12"/>
+    </row>
+    <row r="66" spans="21:27" x14ac:dyDescent="0.2">
+      <c r="U66" s="12"/>
+      <c r="V66" s="12"/>
+      <c r="W66" s="12"/>
+      <c r="X66" s="12"/>
+      <c r="Y66" s="12"/>
+      <c r="Z66" s="12"/>
+      <c r="AA66" s="12"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A9:W15 A17:W17">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>A$8="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:W42">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>A$25="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10647,15 +15060,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02199C31-48B1-490B-A194-08D98129BC48}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED3A4330-F882-48EB-84A6-4C413EAC9C8A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2715bc29-68cb-4af3-883a-7773fe7844be"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10679,17 +15103,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED3A4330-F882-48EB-84A6-4C413EAC9C8A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02199C31-48B1-490B-A194-08D98129BC48}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2715bc29-68cb-4af3-883a-7773fe7844be"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>